--- a/templates/xlsx/hypothesis-ledger.xlsx
+++ b/templates/xlsx/hypothesis-ledger.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hypothesis Ledger" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>

--- a/templates/xlsx/hypothesis-ledger.xlsx
+++ b/templates/xlsx/hypothesis-ledger.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading with selling point B lifts 3s retention ≥40% for parents</t>
+          <t>Leading with selling point B lifts 6s retention ≥60% for parents</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;25% after 6 videos</t>
+          <t>&lt;40% after 6 videos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>≥40% and ≥5 orders</t>
+          <t>≥60% and ≥5 orders</t>
         </is>
       </c>
       <c r="I2" t="n">
